--- a/business_surveys/026_retention_strategy_report_form--business_surveys.xlsx
+++ b/business_surveys/026_retention_strategy_report_form--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Customer Segment</t>
+          <t>Customer Segment Options</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Reasons for Churn</t>
+          <t>Reasons For Churn Options</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Retention Strategy</t>
+          <t>Retention Strategy Options</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Customer Interaction</t>
+          <t>Customer Interaction Details</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_1_month'}</t>
+          <t>less_than_1_month</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less than 1 month'}</t>
+          <t>Less than 1 month</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'1-3_months'}</t>
+          <t>1-3_months</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '1-3 months'}</t>
+          <t>1-3 months</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'3-6_months'}</t>
+          <t>3-6_months</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '3-6 months'}</t>
+          <t>3-6 months</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'more_than_6_months'}</t>
+          <t>more_than_6_months</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'More than 6 months'}</t>
+          <t>More than 6 months</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
